--- a/単元_素顔同盟_私/教員用評価シート.xlsx
+++ b/単元_素顔同盟_私/教員用評価シート.xlsx
@@ -56,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +98,11 @@
         <fgColor rgb="00FFFFF0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -125,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -171,6 +176,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -575,7 +586,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>■ 単元目標：カギカッコに入れられた語などの働きに注意して語感を捉えながら、二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
+          <t>■ 単元目標：カギカッコに入れられた語などの働きに注意して語感を捉えながら、自分で選んだ（または自分で立てた）観点から二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1236,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1341,16 +1352,25 @@
       </c>
       <c r="B13" s="13" t="n"/>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>★ B/Aの分水嶺：条件①（両作品からの引用）と条件②（「しかし／とはいえ」の疑いの一文）の両方に触れていなければA以上にしない。このルールはGASの採点プロンプトにも埋め込んである。</t>
+          <t>★ B/Aの分水嶺：条件①（自分の観点を示し、その観点から両作品を引用）と条件②（「しかし／とはいえ」の疑いの一文）の両方に触れていなければA以上にしない。このルールはGASの採点プロンプトにも埋め込んである。</t>
         </is>
       </c>
       <c r="B15" s="14" t="n"/>
     </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>★ 観点は生徒が自分で決める（必修は「批評・評価」1つだけ）。AIには「生徒の観点を別の観点に置きかえる提案はしない」よう指示している。観点そのものの当否は評価しない。評価するのは、その観点から根拠を示して吟味できているかである。</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A15:B15"/>
@@ -1365,23 +1385,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>協議見取り記録（第5・6・7時）　――「主体的に学習に取り組む態度」の評価材</t>
+          <t>協議見取り記録（第2時・第5〜7時）　――「主体的に学習に取り組む態度」の評価材／班編成のもとになる表</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1391,11 +1413,13 @@
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>A＝提案者として本文の根拠を示して読みを述べ、他者の異なる読みを受けて自分の考えを述べ直している　／　B＝提案者の役割を果たし、他のラウンドでも質問か反論を述べている　／　C＝提案メモ未記入、または発言なし</t>
+          <t>A＝自分で観点を選び（立て）、その観点から根拠を示して提案し、他の観点からの指摘を受けて読みを述べ直している　／　B＝自分で観点を決め、提案者の役割を果たし、他のラウンドでも質問か反論を述べている　／　C＝観点が未記入、提案メモ未記入、または発言なし</t>
         </is>
       </c>
       <c r="B2" s="15" t="n"/>
@@ -1405,457 +1429,567 @@
       <c r="F2" s="15" t="n"/>
       <c r="G2" s="15" t="n"/>
       <c r="H2" s="15" t="n"/>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>★ E列「選んだ観点」は第2時のおわりに記入する。これを見て【観点がばらけるように】班を組む。9観点に無い観点を自分で立てた生徒はF列に「自」と入れる（その生徒は各班に散らすと議論が立ち上がる）。</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>クラス</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>出席番号</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>班</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>提案した論題</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>提案の要点（教師メモ）</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>他者の読みを受けて述べ直した箇所</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>選んだ観点（第2時）</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>自立
+観点</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>提案した論題／提案の要点</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>自分の観点では見えなかったこと（第6時）</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>他の観点を受けて述べ直した箇所</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>態度
 A/B/C</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="9" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="4" t="n"/>
       <c r="G5" s="5" t="n"/>
-      <c r="H5" s="9" t="n"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="4" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="9" t="n"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="4" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="9" t="n"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="4" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="9" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="4" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="9" t="n"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="4" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="4" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="4" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="4" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="9" t="n"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="4" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="4" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="4" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="4" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="28" customHeight="1">
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="4" t="n"/>
       <c r="G19" s="5" t="n"/>
-      <c r="H19" s="9" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="4" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="4" t="n"/>
       <c r="G21" s="5" t="n"/>
-      <c r="H21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="n"/>
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="4" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="n"/>
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="5" t="n"/>
-      <c r="H23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="28" customHeight="1">
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="4" t="n"/>
       <c r="G24" s="5" t="n"/>
-      <c r="H24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="n"/>
       <c r="B25" s="4" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="4" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="9" t="n"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="4" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="4" t="n"/>
       <c r="G26" s="5" t="n"/>
-      <c r="H26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="4" t="n"/>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="4" t="n"/>
       <c r="G27" s="5" t="n"/>
-      <c r="H27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1">
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="4" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="n"/>
       <c r="B29" s="4" t="n"/>
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="4" t="n"/>
       <c r="G29" s="5" t="n"/>
-      <c r="H29" s="9" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="n"/>
       <c r="B30" s="4" t="n"/>
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="5" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="4" t="n"/>
       <c r="G30" s="5" t="n"/>
-      <c r="H30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1">
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="n"/>
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="4" t="n"/>
       <c r="G31" s="5" t="n"/>
-      <c r="H31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="28" customHeight="1">
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="n"/>
       <c r="B32" s="4" t="n"/>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="4" t="n"/>
       <c r="G32" s="5" t="n"/>
-      <c r="H32" s="9" t="n"/>
-    </row>
-    <row r="33" ht="28" customHeight="1">
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="n"/>
       <c r="B33" s="4" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="5" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="4" t="n"/>
       <c r="G33" s="5" t="n"/>
-      <c r="H33" s="9" t="n"/>
-    </row>
-    <row r="34" ht="28" customHeight="1">
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="n"/>
       <c r="B34" s="4" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="5" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="4" t="n"/>
       <c r="G34" s="5" t="n"/>
-      <c r="H34" s="9" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1">
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="n"/>
       <c r="B35" s="4" t="n"/>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="5" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="4" t="n"/>
       <c r="G35" s="5" t="n"/>
-      <c r="H35" s="9" t="n"/>
-    </row>
-    <row r="36" ht="28" customHeight="1">
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="n"/>
       <c r="B36" s="4" t="n"/>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="5" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="4" t="n"/>
       <c r="G36" s="5" t="n"/>
-      <c r="H36" s="9" t="n"/>
-    </row>
-    <row r="37" ht="28" customHeight="1">
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="n"/>
       <c r="B37" s="4" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="5" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="4" t="n"/>
       <c r="G37" s="5" t="n"/>
-      <c r="H37" s="9" t="n"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="n"/>
       <c r="B38" s="4" t="n"/>
       <c r="C38" s="5" t="n"/>
       <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="5" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="4" t="n"/>
       <c r="G38" s="5" t="n"/>
-      <c r="H38" s="9" t="n"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="9" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="4" t="n"/>
       <c r="B39" s="4" t="n"/>
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="5" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="4" t="n"/>
       <c r="G39" s="5" t="n"/>
-      <c r="H39" s="9" t="n"/>
-    </row>
-    <row r="40" ht="28" customHeight="1">
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="n"/>
       <c r="B40" s="4" t="n"/>
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="5" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="4" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="H40" s="9" t="n"/>
-    </row>
-    <row r="41" ht="28" customHeight="1">
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="9" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="n"/>
       <c r="B41" s="4" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="5" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="4" t="n"/>
       <c r="G41" s="5" t="n"/>
-      <c r="H41" s="9" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1">
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="4" t="n"/>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="5" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="4" t="n"/>
       <c r="G42" s="5" t="n"/>
-      <c r="H42" s="9" t="n"/>
-    </row>
-    <row r="43" ht="28" customHeight="1">
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="9" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="4" t="n"/>
       <c r="B43" s="4" t="n"/>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="5" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="4" t="n"/>
       <c r="G43" s="5" t="n"/>
-      <c r="H43" s="9" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H4:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/単元_素顔同盟_私/教員用評価シート.xlsx
+++ b/単元_素顔同盟_私/教員用評価シート.xlsx
@@ -556,7 +556,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -568,7 +568,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>教員用評価シート　「私」を消すもの、「私」を支えるもの ――「素顔同盟」「私」を批判的に読む（中3・全7時間）</t>
+          <t>教員用評価シート　「私」を消すもの、「私」を支えるもの（中3・全7時間／まとめ＝グループディスカッション）</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -586,7 +586,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>■ 単元目標：カギカッコに入れられた語などの働きに注意して語感を捉えながら、自分で選んだ（または自分で立てた）観点から二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
+          <t>■ 単元目標：カギカッコに入れた語などの働きに注意して語感を捉えながら、自分で決めた観点から二つの作品を批判的に読み、文章に表れたものの見方や考え方について、根拠を示してグループで話し合うことができる。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>批評文（800字）★AI採点対象</t>
+          <t>ディスカッションを終えて（300字）★AI採点対象</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>批評文（F列）</t>
+          <t>ディスカッションを終えて（F列・300字）</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>5段階（S/A/B/C/D）　※批評文をAIが一次採点</t>
+          <t>5段階（S/A/B/C/D）　※300字をAIが一次採点。話し合いそのものは「協議見取り」で見る</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>★ B/Aの分水嶺：条件①（自分の観点を示し、その観点から両作品を引用）と条件②（「しかし／とはいえ」の疑いの一文）の両方に触れていなければA以上にしない。このルールはGASの採点プロンプトにも埋め込んである。</t>
+          <t>★ B/Aの分水嶺：条件①（自分の観点と本文の根拠で主張した）と条件②（他の観点を受けて考えを見直した）の両方がなければA以上にしない。GASの採点プロンプトにも同じルールを埋め込んである。</t>
         </is>
       </c>
       <c r="B15" s="14" t="n"/>
@@ -1416,10 +1416,10 @@
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>A＝自分で観点を選び（立て）、その観点から根拠を示して提案し、他の観点からの指摘を受けて読みを述べ直している　／　B＝自分で観点を決め、提案者の役割を果たし、他のラウンドでも質問か反論を述べている　／　C＝観点が未記入、提案メモ未記入、または発言なし</t>
+          <t>★ 単元のまとめは【グループディスカッション】。話し合いそのものの評価はこのシートで行う（F列の300字はAIの一次採点）。　A＝自分で観点を決め、根拠を示して提案し、他の観点を受けて読みを述べ直した　／　B＝自分で観点を決め、提案者をつとめ、他の回でも質問か反論をした　／　C＝観点・提案メモ未記入、または発言なし</t>
         </is>
       </c>
       <c r="B2" s="15" t="n"/>
@@ -1432,10 +1432,10 @@
       <c r="I2" s="15" t="n"/>
       <c r="J2" s="15" t="n"/>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>★ E列「選んだ観点」は第2時のおわりに記入する。これを見て【観点がばらけるように】班を組む。9観点に無い観点を自分で立てた生徒はF列に「自」と入れる（その生徒は各班に散らすと議論が立ち上がる）。</t>
+          <t>★ E列は2時のおわりに記入。これを見て【観点がばらけるように】班を組む。自分で観点を作った生徒はF列に「自」（各班に散らす）。論題は3つ。5時に1周目（論題1→2→3）、6時に2周目（同じ3論題を問い直す）。6ラウンドで1人1回提案者。</t>
         </is>
       </c>
       <c r="B3" s="16" t="n"/>
@@ -1471,23 +1471,23 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>選んだ観点（第2時）</t>
+          <t>選んだ観点（2時）</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>自立
+          <t>自作
 観点</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>提案した論題／提案の要点</t>
+          <t>提案した論題（1・2・3）／提案の要点</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>自分の観点では見えなかったこと（第6時）</t>
+          <t>見えなかったこと（6時）</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">

--- a/単元_素顔同盟_私/教員用評価シート.xlsx
+++ b/単元_素顔同盟_私/教員用評価シート.xlsx
@@ -1385,19 +1385,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1414,7 +1413,6 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
@@ -1430,12 +1428,11 @@
       <c r="G2" s="15" t="n"/>
       <c r="H2" s="15" t="n"/>
       <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="n"/>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>★ E列は2時のおわりに記入。これを見て【観点がばらけるように】班を組む。自分で観点を作った生徒はF列に「自」（各班に散らす）。論題は3つ。5時に1周目（論題1→2→3）、6時に2周目（同じ3論題を問い直す）。6ラウンドで1人1回提案者。</t>
+          <t>★ E列は2時のおわりに記入。これを見て【観点がばらけるように】班を組む。観点は9つから選ばせる（必修は「批評・評価」）。論題は3つ。5時に1周目（論題1→2→3）、6時に2周目（同じ3論題を問い直す）。6ラウンドで1人1回提案者。</t>
         </is>
       </c>
       <c r="B3" s="16" t="n"/>
@@ -1446,7 +1443,6 @@
       <c r="G3" s="16" t="n"/>
       <c r="H3" s="16" t="n"/>
       <c r="I3" s="16" t="n"/>
-      <c r="J3" s="16" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1476,26 +1472,20 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>自作
-観点</t>
+          <t>提案した論題（1・2・3）／提案の要点</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>提案した論題（1・2・3）／提案の要点</t>
+          <t>見えなかったこと（6時）</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>見えなかったこと（6時）</t>
+          <t>他の観点を受けて述べ直した箇所</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>他の観点を受けて述べ直した箇所</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>態度
 A/B/C</t>
@@ -1508,11 +1498,10 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="17" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n"/>
@@ -1520,11 +1509,10 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="17" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
@@ -1532,11 +1520,10 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="17" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="n"/>
@@ -1544,11 +1531,10 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="17" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="n"/>
@@ -1556,11 +1542,10 @@
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="17" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="n"/>
@@ -1568,11 +1553,10 @@
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="17" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="4" t="n"/>
@@ -1580,11 +1564,10 @@
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="17" t="n"/>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="n"/>
@@ -1592,11 +1575,10 @@
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="17" t="n"/>
-      <c r="F12" s="4" t="n"/>
+      <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4" t="n"/>
@@ -1604,11 +1586,10 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="17" t="n"/>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="n"/>
@@ -1616,11 +1597,10 @@
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="17" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="n"/>
@@ -1628,11 +1608,10 @@
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="17" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="n"/>
@@ -1640,11 +1619,10 @@
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="17" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="n"/>
@@ -1652,11 +1630,10 @@
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="17" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="n"/>
@@ -1664,11 +1641,10 @@
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="17" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="n"/>
@@ -1676,11 +1652,10 @@
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="17" t="n"/>
-      <c r="F19" s="4" t="n"/>
+      <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="n"/>
@@ -1688,11 +1663,10 @@
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="17" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="n"/>
@@ -1700,11 +1674,10 @@
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="17" t="n"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="n"/>
@@ -1712,11 +1685,10 @@
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="17" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="n"/>
@@ -1724,11 +1696,10 @@
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="17" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="n"/>
@@ -1736,11 +1707,10 @@
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="17" t="n"/>
-      <c r="F24" s="4" t="n"/>
+      <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="n"/>
@@ -1748,11 +1718,10 @@
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="17" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="n"/>
@@ -1760,11 +1729,10 @@
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="17" t="n"/>
-      <c r="F26" s="4" t="n"/>
+      <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="n"/>
@@ -1772,11 +1740,10 @@
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="17" t="n"/>
-      <c r="F27" s="4" t="n"/>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="n"/>
@@ -1784,11 +1751,10 @@
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="17" t="n"/>
-      <c r="F28" s="4" t="n"/>
+      <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="9" t="n"/>
+      <c r="I28" s="9" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="n"/>
@@ -1796,11 +1762,10 @@
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="17" t="n"/>
-      <c r="F29" s="4" t="n"/>
+      <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="n"/>
@@ -1808,11 +1773,10 @@
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="17" t="n"/>
-      <c r="F30" s="4" t="n"/>
+      <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="n"/>
@@ -1820,11 +1784,10 @@
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="17" t="n"/>
-      <c r="F31" s="4" t="n"/>
+      <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="n"/>
@@ -1832,11 +1795,10 @@
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="17" t="n"/>
-      <c r="F32" s="4" t="n"/>
+      <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="n"/>
@@ -1844,11 +1806,10 @@
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="17" t="n"/>
-      <c r="F33" s="4" t="n"/>
+      <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="n"/>
@@ -1856,11 +1817,10 @@
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="17" t="n"/>
-      <c r="F34" s="4" t="n"/>
+      <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="n"/>
@@ -1868,11 +1828,10 @@
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="17" t="n"/>
-      <c r="F35" s="4" t="n"/>
+      <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="n"/>
@@ -1880,11 +1839,10 @@
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="17" t="n"/>
-      <c r="F36" s="4" t="n"/>
+      <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="n"/>
@@ -1892,11 +1850,10 @@
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="17" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="n"/>
@@ -1904,11 +1861,10 @@
       <c r="C38" s="5" t="n"/>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="17" t="n"/>
-      <c r="F38" s="4" t="n"/>
+      <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="4" t="n"/>
@@ -1916,11 +1872,10 @@
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="17" t="n"/>
-      <c r="F39" s="4" t="n"/>
+      <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="9" t="n"/>
+      <c r="I39" s="9" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="n"/>
@@ -1928,11 +1883,10 @@
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="17" t="n"/>
-      <c r="F40" s="4" t="n"/>
+      <c r="F40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
       <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="n"/>
@@ -1940,11 +1894,10 @@
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="17" t="n"/>
-      <c r="F41" s="4" t="n"/>
+      <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
       <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="4" t="n"/>
@@ -1952,11 +1905,10 @@
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="17" t="n"/>
-      <c r="F42" s="4" t="n"/>
+      <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="9" t="n"/>
+      <c r="I42" s="9" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="4" t="n"/>
@@ -1964,11 +1916,10 @@
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="17" t="n"/>
-      <c r="F43" s="4" t="n"/>
+      <c r="F43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="4" t="n"/>
@@ -1976,20 +1927,19 @@
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="17" t="n"/>
-      <c r="F44" s="4" t="n"/>
+      <c r="F44" s="5" t="n"/>
       <c r="G44" s="5" t="n"/>
       <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/単元_素顔同盟_私/教員用評価シート.xlsx
+++ b/単元_素顔同盟_私/教員用評価シート.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,12 +30,17 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="15"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -51,9 +56,8 @@
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="10">
@@ -75,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8DAEF"/>
+        <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
+        <fgColor rgb="00E8DAEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,50 +142,56 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,24 +558,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>教員用評価シート　「私」を消すもの、「私」を支えるもの（中3・全7時間／まとめ＝グループディスカッション）</t>
@@ -582,11 +593,12 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="34" customHeight="1">
+      <c r="M1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>■ 単元目標：カギカッコに入れた語などの働きに注意して語感を捉えながら、自分で決めた観点から二つの作品を批判的に読み、文章に表れたものの見方や考え方について、根拠を示してグループで話し合うことができる。</t>
+          <t>目標：自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -600,640 +612,707 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="34" customHeight="1">
+      <c r="M2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>★ 思考・判断・表現は【D〜G列の記述】と【当日の発言（「協議見取り」シート）】を合わせてJ列で確定する。H列のAI評価は記述だけを見た暫定値。</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>クラス</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>出席番号</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>発問①（知技・語感／150〜200字）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>発問②（思判表・仮定判断／200〜250字）</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ディスカッションを終えて（300字）★AI採点対象</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>論題1 仮面とデータは同じものか</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>論題2 どちらの語り手が危ういか</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>論題3 「私」を支えるものを示せているか</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>見直し（200字）</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>AI評価
-S/A/B/C/D</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+（記述のみ暫定）</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>AIコメント</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>教師最終評価</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>★教師最終評価
+（記述＋発言）</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>自己評価</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>評価差考察</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>ふりかえり</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="8" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-    </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="8" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="8" t="n"/>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="10" t="n"/>
-      <c r="L7" s="10" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="10" t="n"/>
-      <c r="L8" s="10" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="8" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="n"/>
-      <c r="L9" s="10" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="10" t="n"/>
-      <c r="L10" s="10" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="10" t="n"/>
-      <c r="L11" s="10" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="n"/>
-      <c r="L15" s="10" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n"/>
-      <c r="L16" s="10" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="11" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="11" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="11" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="11" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="8" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="10" t="n"/>
-      <c r="L23" s="10" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n"/>
-      <c r="L24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="11" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="10" t="n"/>
-      <c r="L25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="10" t="n"/>
-      <c r="L26" s="10" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="11" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="10" t="n"/>
-      <c r="L29" s="10" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="10" t="n"/>
-      <c r="L30" s="10" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="8" t="n"/>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="10" t="n"/>
-      <c r="L31" s="10" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="8" t="n"/>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="10" t="n"/>
-      <c r="L32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="10" t="n"/>
-      <c r="L33" s="10" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="7" t="n"/>
       <c r="I34" s="8" t="n"/>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n"/>
-      <c r="L34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="11" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="8" t="n"/>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="10" t="n"/>
-      <c r="L35" s="10" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="8" t="n"/>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="10" t="n"/>
-      <c r="L36" s="10" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="11" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="8" t="n"/>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="11" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="7" t="n"/>
       <c r="I38" s="8" t="n"/>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n"/>
-      <c r="L38" s="10" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="11" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="8" t="n"/>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="8" t="n"/>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="11" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="8" t="n"/>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="10" t="n"/>
-      <c r="L41" s="10" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="11" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="n"/>
       <c r="I42" s="8" t="n"/>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="11" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="8" t="n"/>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="11" t="n"/>
+      <c r="M44" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="G4:G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1247,11 +1326,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1263,117 +1342,126 @@
       <c r="B1" s="1" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>AIモデル</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>gemini-2.0-flash</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>評価対象</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>ディスカッションを終えて（F列・300字）</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>論題1〜3の記述（D〜F列）＋見直し（G列）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>評価観点</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>思考・判断・表現のみ　5段階（S/A/B/C/D）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>知識・技能</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>3段階（A/B/C）　※発問①を教師が見取る（AI採点対象外）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>思考・判断・表現</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>5段階（S/A/B/C/D）　※300字をAIが一次採点。話し合いそのものは「協議見取り」で見る</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>この単元では評価しない（学期内の他単元・定期テストで見る）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>データ範囲</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>4行目〜43行目</t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>5行目〜44行目</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>ClassroomフォルダID</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>（ここにフォルダIDを入力）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>★ APIキーは このシートに書かない。GASの「スクリプト プロパティ」に GEMINI_API_KEY として登録する。</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>★ B/Aの分水嶺：条件①（自分の観点と本文の根拠で主張した）と条件②（他の観点を受けて考えを見直した）の両方がなければA以上にしない。GASの採点プロンプトにも同じルールを埋め込んである。</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n"/>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>★ 観点は生徒が自分で決める（必修は「批評・評価」1つだけ）。AIには「生徒の観点を別の観点に置きかえる提案はしない」よう指示している。観点そのものの当否は評価しない。評価するのは、その観点から根拠を示して吟味できているかである。</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n"/>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>★ APIキーはこのシートに書かない。GASの「スクリプト プロパティ」に GEMINI_API_KEY として登録する。</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>★ B/Aの分水嶺：条件①（3つの論題すべてを観点と本文の根拠でまとめた）と条件②（当日、自分の観点から根拠を示して発言した）の両方がなければA以上にしない。</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n"/>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>★ AIは条件②（当日の発言）を判定できない。H列は記述だけを見た暫定評価。「協議見取り」シートのH列（発言の判定）と合わせて、J列で最終評価を確定する。</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>★ 観点は9つから生徒が選ぶ（必修は「批評・評価」）。どの観点を選んだかで評価を変えない。AIにも「別の観点をすすめない」と指示済み。</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A17:B17"/>
+  <mergeCells count="5">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1385,24 +1473,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>協議見取り記録（第2時・第5〜7時）　――「主体的に学習に取り組む態度」の評価材／班編成のもとになる表</t>
+          <t>協議見取り記録（2時・5〜7時）　―― 当日の発言を評価する表。思判表の条件②と、態度の評価材</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1413,79 +1502,89 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>★ 単元のまとめは【グループディスカッション】。話し合いそのものの評価はこのシートで行う（F列の300字はAIの一次採点）。　A＝自分で観点を決め、根拠を示して提案し、他の観点を受けて読みを述べ直した　／　B＝自分で観点を決め、提案者をつとめ、他の回でも質問か反論をした　／　C＝観点・提案メモ未記入、または発言なし</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="15" t="n"/>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="15" t="n"/>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>★ E列は2時のおわりに記入。これを見て【観点がばらけるように】班を組む。観点は9つから選ばせる（必修は「批評・評価」）。論題は3つ。5時に1周目（論題1→2→3）、6時に2周目（同じ3論題を問い直す）。6ラウンドで1人1回提案者。</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16" t="n"/>
-      <c r="H3" s="16" t="n"/>
-      <c r="I3" s="16" t="n"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>★ 発話は残らない。ここを書かないと条件②（当日の発言）と態度の評価材が無くなる。5・6時は巡回しながらF〜J列を埋める。全発言を聞き取る必要はない。</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>★ E列は2時のおわりに記入し、【観点がばらけるように】班を組む。論題は3つで、3つとも二作にまたがる。発表する論題は当日に知らせる（生徒は3つ全部準備している）。</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="17" t="n"/>
+      <c r="H3" s="17" t="n"/>
+      <c r="I3" s="17" t="n"/>
+      <c r="J3" s="17" t="n"/>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>クラス</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>出席番号</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>班</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>選んだ観点（2時）</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>提案した論題（1・2・3）／提案の要点</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>見えなかったこと（6時）</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>他の観点を受けて述べ直した箇所</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>発表した
+論題</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>当日の発言の要点</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>条件②
+○△×</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>見えなかったこと／述べ直した箇所</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>態度
 A/B/C</t>
@@ -1493,454 +1592,514 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="18" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="9" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="10" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="17" t="n"/>
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="18" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="9" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="10" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="18" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="9" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="10" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="17" t="n"/>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="18" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="9" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="10" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="18" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="9" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="10" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="17" t="n"/>
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="18" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="9" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="10" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="17" t="n"/>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="18" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="9" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="10" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="17" t="n"/>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="18" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="9" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="10" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="18" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="9" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="10" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="17" t="n"/>
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="18" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="9" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="10" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="17" t="n"/>
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="18" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="9" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="10" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="17" t="n"/>
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="18" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="9" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="10" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="17" t="n"/>
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="18" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="9" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="10" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="18" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="9" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="10" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="18" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="9" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="10" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="18" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="9" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="10" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="18" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="9" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="10" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="18" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="9" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="10" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="18" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="9" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="10" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="18" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="9" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="10" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="18" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="9" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="10" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="18" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="9" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="10" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="18" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="9" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="10" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="17" t="n"/>
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="18" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="9" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="10" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="17" t="n"/>
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="18" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="9" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="10" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="17" t="n"/>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="18" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="9" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="10" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="17" t="n"/>
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="18" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="9" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="10" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="17" t="n"/>
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="18" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="9" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="10" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="17" t="n"/>
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="18" t="n"/>
       <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="9" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="10" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="17" t="n"/>
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="18" t="n"/>
       <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="9" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="10" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="17" t="n"/>
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="18" t="n"/>
       <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="9" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="10" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="17" t="n"/>
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="18" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="9" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="10" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="17" t="n"/>
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="18" t="n"/>
       <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="9" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="10" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="17" t="n"/>
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="18" t="n"/>
       <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="9" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="10" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="17" t="n"/>
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="18" t="n"/>
       <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="9" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="10" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="17" t="n"/>
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="18" t="n"/>
       <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="9" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="10" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="17" t="n"/>
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="18" t="n"/>
       <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="9" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="10" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="17" t="n"/>
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="18" t="n"/>
       <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="9" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="10" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="17" t="n"/>
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="18" t="n"/>
       <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="9" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="10" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="17" t="n"/>
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="18" t="n"/>
       <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="9" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="10" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>条件②の目安　○＝自分の観点を示し、本文の根拠を引いて主張した　△＝発言したが根拠が本文に届かない　×＝発言していない</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="19" t="n"/>
+      <c r="J46" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="I5:I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="J5:J44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"○,△,×"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/単元_素顔同盟_私/教員用評価シート.xlsx
+++ b/単元_素顔同盟_私/教員用評価シート.xlsx
@@ -656,12 +656,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>論題2 どちらの語り手が危ういか</t>
+          <t>論題2 訴えた人は、救われたか</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>論題3 「私」を支えるものを示せているか</t>
+          <t>論題3 続けさせているのは、誰か</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>★ E列は2時のおわりに記入し、【観点がばらけるように】班を組む。論題は3つで、3つとも二作にまたがる。発表する論題は当日に知らせる（生徒は3つ全部準備している）。</t>
+          <t>★ E列は2時のおわりに記入し、【観点がばらけるように】班を組む。論題は3つ。1=仮面とデータは同じものか／2=訴えた人は救われたか／3=続けさせているのは誰か。いずれも二作にまたがる。発表する論題は当日に知らせる（生徒は3つ全部準備している）。</t>
         </is>
       </c>
       <c r="B3" s="17" t="n"/>

--- a/単元_素顔同盟_私/教員用評価シート.xlsx
+++ b/単元_素顔同盟_私/教員用評価シート.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -183,6 +183,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -598,7 +601,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>目標：自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
+          <t>目標：自分で決めた観点から二つの作品を批判的に読みながら、三つの論題について、文章に表れているものの見方や考え方について考えることができる。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1326,7 +1329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1455,8 +1458,41 @@
       </c>
       <c r="B19" s="16" t="n"/>
     </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>評価規準（思判表）</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>「読むこと」において、文章を批判的に読みながら、文章に表れているものの見方や考え方について考えている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>評価規準（態度）</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>積極的に文章を批判的に読み、学習課題に沿って、考えたことを互いに伝え合おうとしている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>★ 観点別評価への読みかえ（指導要録はA・B・Cの3段階）　S・A → A（十分満足できる）／B → B（おおむね満足できる）／C・D → C（努力を要する）。生徒への返却はS〜Dのまま。</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A13:B13"/>
@@ -1521,20 +1557,20 @@
       <c r="J2" s="3" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>★ E列は2時のおわりに記入し、【観点がばらけるように】班を組む。論題は3つ。1=仮面とデータは同じものか／2=訴えた人は救われたか／3=続けさせているのは誰か。いずれも二作にまたがる。発表する論題は当日に知らせる（生徒は3つ全部準備している）。</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="17" t="n"/>
-      <c r="E3" s="17" t="n"/>
-      <c r="F3" s="17" t="n"/>
-      <c r="G3" s="17" t="n"/>
-      <c r="H3" s="17" t="n"/>
-      <c r="I3" s="17" t="n"/>
-      <c r="J3" s="17" t="n"/>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1596,7 +1632,7 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="18" t="n"/>
+      <c r="E5" s="19" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="7" t="n"/>
@@ -1608,7 +1644,7 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="18" t="n"/>
+      <c r="E6" s="19" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="7" t="n"/>
@@ -1620,7 +1656,7 @@
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="5" t="n"/>
-      <c r="E7" s="18" t="n"/>
+      <c r="E7" s="19" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="7" t="n"/>
@@ -1632,7 +1668,7 @@
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="18" t="n"/>
+      <c r="E8" s="19" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="n"/>
@@ -1644,7 +1680,7 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="18" t="n"/>
+      <c r="E9" s="19" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="7" t="n"/>
@@ -1656,7 +1692,7 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="18" t="n"/>
+      <c r="E10" s="19" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="7" t="n"/>
@@ -1668,7 +1704,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="18" t="n"/>
+      <c r="E11" s="19" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="7" t="n"/>
@@ -1680,7 +1716,7 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="18" t="n"/>
+      <c r="E12" s="19" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="n"/>
@@ -1692,7 +1728,7 @@
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="18" t="n"/>
+      <c r="E13" s="19" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="7" t="n"/>
@@ -1704,7 +1740,7 @@
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="n"/>
-      <c r="E14" s="18" t="n"/>
+      <c r="E14" s="19" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="7" t="n"/>
@@ -1716,7 +1752,7 @@
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="18" t="n"/>
+      <c r="E15" s="19" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="7" t="n"/>
@@ -1728,7 +1764,7 @@
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="18" t="n"/>
+      <c r="E16" s="19" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="7" t="n"/>
@@ -1740,7 +1776,7 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="18" t="n"/>
+      <c r="E17" s="19" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="7" t="n"/>
@@ -1752,7 +1788,7 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="18" t="n"/>
+      <c r="E18" s="19" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="7" t="n"/>
@@ -1764,7 +1800,7 @@
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="18" t="n"/>
+      <c r="E19" s="19" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="7" t="n"/>
@@ -1776,7 +1812,7 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="18" t="n"/>
+      <c r="E20" s="19" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="n"/>
@@ -1788,7 +1824,7 @@
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="18" t="n"/>
+      <c r="E21" s="19" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="7" t="n"/>
@@ -1800,7 +1836,7 @@
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="5" t="n"/>
-      <c r="E22" s="18" t="n"/>
+      <c r="E22" s="19" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="7" t="n"/>
@@ -1812,7 +1848,7 @@
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="5" t="n"/>
-      <c r="E23" s="18" t="n"/>
+      <c r="E23" s="19" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="7" t="n"/>
@@ -1824,7 +1860,7 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="18" t="n"/>
+      <c r="E24" s="19" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="n"/>
@@ -1836,7 +1872,7 @@
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="18" t="n"/>
+      <c r="E25" s="19" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="7" t="n"/>
@@ -1848,7 +1884,7 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="5" t="n"/>
-      <c r="E26" s="18" t="n"/>
+      <c r="E26" s="19" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="n"/>
@@ -1860,7 +1896,7 @@
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="5" t="n"/>
-      <c r="E27" s="18" t="n"/>
+      <c r="E27" s="19" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="7" t="n"/>
@@ -1872,7 +1908,7 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="5" t="n"/>
-      <c r="E28" s="18" t="n"/>
+      <c r="E28" s="19" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="7" t="n"/>
@@ -1884,7 +1920,7 @@
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="18" t="n"/>
+      <c r="E29" s="19" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="7" t="n"/>
@@ -1896,7 +1932,7 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="18" t="n"/>
+      <c r="E30" s="19" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="n"/>
@@ -1908,7 +1944,7 @@
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="5" t="n"/>
-      <c r="E31" s="18" t="n"/>
+      <c r="E31" s="19" t="n"/>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="7" t="n"/>
@@ -1920,7 +1956,7 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="5" t="n"/>
-      <c r="E32" s="18" t="n"/>
+      <c r="E32" s="19" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="n"/>
@@ -1932,7 +1968,7 @@
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="5" t="n"/>
-      <c r="E33" s="18" t="n"/>
+      <c r="E33" s="19" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="7" t="n"/>
@@ -1944,7 +1980,7 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="5" t="n"/>
-      <c r="E34" s="18" t="n"/>
+      <c r="E34" s="19" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="7" t="n"/>
@@ -1956,7 +1992,7 @@
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="18" t="n"/>
+      <c r="E35" s="19" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="7" t="n"/>
@@ -1968,7 +2004,7 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="18" t="n"/>
+      <c r="E36" s="19" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="7" t="n"/>
@@ -1980,7 +2016,7 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="18" t="n"/>
+      <c r="E37" s="19" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="7" t="n"/>
@@ -1992,7 +2028,7 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="5" t="n"/>
-      <c r="E38" s="18" t="n"/>
+      <c r="E38" s="19" t="n"/>
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="7" t="n"/>
@@ -2004,7 +2040,7 @@
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="5" t="n"/>
-      <c r="E39" s="18" t="n"/>
+      <c r="E39" s="19" t="n"/>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="7" t="n"/>
@@ -2016,7 +2052,7 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="5" t="n"/>
-      <c r="E40" s="18" t="n"/>
+      <c r="E40" s="19" t="n"/>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="7" t="n"/>
@@ -2028,7 +2064,7 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="5" t="n"/>
-      <c r="E41" s="18" t="n"/>
+      <c r="E41" s="19" t="n"/>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="7" t="n"/>
@@ -2040,7 +2076,7 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="5" t="n"/>
-      <c r="E42" s="18" t="n"/>
+      <c r="E42" s="19" t="n"/>
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="n"/>
@@ -2052,7 +2088,7 @@
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="5" t="n"/>
-      <c r="E43" s="18" t="n"/>
+      <c r="E43" s="19" t="n"/>
       <c r="F43" s="5" t="n"/>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="7" t="n"/>
@@ -2064,7 +2100,7 @@
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="5" t="n"/>
-      <c r="E44" s="18" t="n"/>
+      <c r="E44" s="19" t="n"/>
       <c r="F44" s="5" t="n"/>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="7" t="n"/>
@@ -2072,20 +2108,20 @@
       <c r="J44" s="10" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>条件②の目安　○＝自分の観点を示し、本文の根拠を引いて主張した　△＝発言したが根拠が本文に届かない　×＝発言していない</t>
         </is>
       </c>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="19" t="n"/>
-      <c r="F46" s="19" t="n"/>
-      <c r="G46" s="19" t="n"/>
-      <c r="H46" s="19" t="n"/>
-      <c r="I46" s="19" t="n"/>
-      <c r="J46" s="19" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="20" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="20" t="n"/>
+      <c r="J46" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/単元_素顔同盟_私/教員用評価シート.xlsx
+++ b/単元_素顔同盟_私/教員用評価シート.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,9 +164,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -181,9 +178,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -192,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -561,22 +558,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -597,6 +595,7 @@
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -616,11 +615,12 @@
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>★ 思考・判断・表現は【D〜G列の記述】と【当日の発言（「協議見取り」シート）】を合わせてJ列で確定する。H列のAI評価は記述だけを見た暫定値。</t>
+          <t>★ 思考・判断・表現は【D〜J列の記述】と【当日の発言（「協議見取り」シート）】を合わせてM列で確定する。K列のAI評価は記述だけを見た暫定値。生徒シートへの自動返却は行わない（評価は口頭または紙で返す）。</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -635,6 +635,7 @@
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -654,52 +655,57 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>選んだ観点</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>論題1 仮面とデータは同じものか</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>論題2 訴えた人は、救われたか</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>論題3 続けさせているのは、誰か</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>見直し（200字）</t>
-        </is>
-      </c>
       <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>聞いて考えた①</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>聞いて考えた②</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>聞いて考えた③</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>AI評価
 （記述のみ暫定）</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>AIコメント</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>★教師最終評価
 （記述＋発言）</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>自己評価</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>評価差考察</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>ふりかえり</t>
         </is>
@@ -713,12 +719,13 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="10" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="n"/>
@@ -728,12 +735,13 @@
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="10" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="n"/>
@@ -743,12 +751,13 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="10" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="n"/>
@@ -758,12 +767,13 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="10" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="n"/>
@@ -773,12 +783,13 @@
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="10" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="n"/>
@@ -788,12 +799,13 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="10" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="n"/>
@@ -803,12 +815,13 @@
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="10" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="n"/>
@@ -818,12 +831,13 @@
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="10" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="n"/>
@@ -833,12 +847,13 @@
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="10" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="n"/>
@@ -848,12 +863,13 @@
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="10" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="n"/>
@@ -863,12 +879,13 @@
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="10" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="n"/>
@@ -878,12 +895,13 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="10" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="n"/>
@@ -893,12 +911,13 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="10" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="n"/>
@@ -908,12 +927,13 @@
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="10" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="n"/>
@@ -923,12 +943,13 @@
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="10" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="n"/>
@@ -938,12 +959,13 @@
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="10" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="n"/>
@@ -953,12 +975,13 @@
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="10" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="n"/>
@@ -968,12 +991,13 @@
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="11" t="n"/>
-      <c r="M22" s="11" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="10" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="n"/>
@@ -983,12 +1007,13 @@
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="10" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="n"/>
@@ -998,12 +1023,13 @@
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="11" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="10" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="n"/>
@@ -1013,12 +1039,13 @@
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="11" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="10" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="n"/>
@@ -1028,12 +1055,13 @@
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="11" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="10" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="n"/>
@@ -1043,12 +1071,13 @@
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="11" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="10" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="n"/>
@@ -1058,12 +1087,13 @@
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="11" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="10" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="n"/>
@@ -1073,12 +1103,13 @@
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="6" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="10" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="n"/>
@@ -1088,12 +1119,13 @@
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="11" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="10" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="n"/>
@@ -1103,12 +1135,13 @@
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="10" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="n"/>
@@ -1118,12 +1151,13 @@
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="10" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="n"/>
@@ -1133,12 +1167,13 @@
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="10" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="n"/>
@@ -1148,12 +1183,13 @@
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="11" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="10" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="n"/>
@@ -1163,12 +1199,13 @@
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="10" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="n"/>
@@ -1178,12 +1215,13 @@
       <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="10" t="n"/>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="11" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="10" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="n"/>
@@ -1193,12 +1231,13 @@
       <c r="E37" s="6" t="n"/>
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="10" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="n"/>
@@ -1208,12 +1247,13 @@
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="11" t="n"/>
-      <c r="M38" s="11" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="10" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="n"/>
@@ -1223,12 +1263,13 @@
       <c r="E39" s="6" t="n"/>
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="n"/>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="11" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="10" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="n"/>
@@ -1238,12 +1279,13 @@
       <c r="E40" s="6" t="n"/>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="11" t="n"/>
-      <c r="M40" s="11" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="10" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="n"/>
@@ -1253,12 +1295,13 @@
       <c r="E41" s="6" t="n"/>
       <c r="F41" s="6" t="n"/>
       <c r="G41" s="6" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="10" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="n"/>
@@ -1268,12 +1311,13 @@
       <c r="E42" s="6" t="n"/>
       <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="11" t="n"/>
-      <c r="M42" s="11" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="10" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="n"/>
@@ -1283,12 +1327,13 @@
       <c r="E43" s="6" t="n"/>
       <c r="F43" s="6" t="n"/>
       <c r="G43" s="6" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="10" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="n"/>
@@ -1298,24 +1343,25 @@
       <c r="E44" s="6" t="n"/>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="6" t="n"/>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="11" t="n"/>
-      <c r="M44" s="11" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="8" t="n"/>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1345,150 +1391,150 @@
       <c r="B1" s="1" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>AIモデル</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>gemini-2.0-flash</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="12" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>評価対象</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>論題1〜3の記述（D〜F列）＋見直し（G列）</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>論題1〜3（E〜G列）＋聞いて考えたこと（H〜J列）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>評価観点</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>思考・判断・表現のみ　5段階（S/A/B/C/D）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>知識・技能</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>この単元では評価しない（学期内の他単元・定期テストで見る）</t>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>この単元では評価しない（指導のみ。別単元・定期テストで評価）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>データ範囲</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>5行目〜44行目</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ClassroomフォルダID</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>（ここにフォルダIDを入力）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>★ APIキーはこのシートに書かない。GASの「スクリプト プロパティ」に GEMINI_API_KEY として登録する。</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
+      <c r="B13" s="13" t="n"/>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>★ B/Aの分水嶺：条件①（3つの論題すべてを観点と本文の根拠でまとめた）と条件②（当日、自分の観点から根拠を示して発言した）の両方がなければA以上にしない。</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n"/>
+      <c r="B15" s="14" t="n"/>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>★ AIは条件②（当日の発言）を判定できない。H列は記述だけを見た暫定評価。「協議見取り」シートのH列（発言の判定）と合わせて、J列で最終評価を確定する。</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n"/>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>★ AIは条件②（当日の発言）を判定できない。K列は記述だけを見た暫定評価。「協議見取り」H列（発言の判定）と合わせて、M列で最終評価を確定する。</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>★ 観点は9つから生徒が選ぶ（必修は「批評・評価」）。どの観点を選んだかで評価を変えない。AIにも「別の観点をすすめない」と指示済み。</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>★ 生徒シートに評価を書き戻す機能は無い（生徒シートの「AIの評価と自分の評価」欄を廃止したため）。評価は口頭または紙で返す。</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>評価規準（思判表）</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>「読むこと」において、文章を批判的に読みながら、文章に表れているものの見方や考え方について考えている。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>評価規準（態度）</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>積極的に文章を批判的に読み、学習課題に沿って、考えたことを互いに伝え合おうとしている。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>★ 観点別評価への読みかえ（指導要録はA・B・Cの3段階）　S・A → A（十分満足できる）／B → B（おおむね満足できる）／C・D → C（努力を要する）。生徒への返却はS〜Dのまま。</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
+      <c r="B24" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1556,21 +1602,21 @@
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>★ E列は2時のおわりに記入し、【観点がばらけるように】班を組む。論題は3つ。1=仮面とデータは同じものか／2=訴えた人は救われたか／3=続けさせているのは誰か。いずれも二作にまたがる。発表する論題は当日に知らせる（生徒は3つ全部準備している）。</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="n"/>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="n"/>
-      <c r="F3" s="18" t="n"/>
-      <c r="G3" s="18" t="n"/>
-      <c r="H3" s="18" t="n"/>
-      <c r="I3" s="18" t="n"/>
-      <c r="J3" s="18" t="n"/>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>★ E列は2時のおわりに記入し、【観点がばらけるように】班を組む。観点は9つから選ばせる（必修は「批評・評価」）。論題は3つ。1=仮面とデータは同じものか／2=訴えた人は救われたか／3=続けさせているのは誰か。発表する論題は当日に知らせる（生徒は3つ全部準備している）。</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1600,8 +1646,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>発表した
-論題</t>
+          <t>発表論題</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -1617,7 +1662,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>見えなかったこと／述べ直した箇所</t>
+          <t>ほかの観点を受けて述べ直した箇所</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -1632,496 +1677,496 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="19" t="n"/>
+      <c r="E5" s="17" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="10" t="n"/>
+      <c r="J5" s="18" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="19" t="n"/>
+      <c r="E6" s="17" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="10" t="n"/>
+      <c r="J6" s="18" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="5" t="n"/>
-      <c r="E7" s="19" t="n"/>
+      <c r="E7" s="17" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="6" t="n"/>
-      <c r="J7" s="10" t="n"/>
+      <c r="J7" s="18" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="19" t="n"/>
+      <c r="E8" s="17" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="10" t="n"/>
+      <c r="J8" s="18" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="19" t="n"/>
+      <c r="E9" s="17" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="6" t="n"/>
-      <c r="J9" s="10" t="n"/>
+      <c r="J9" s="18" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="19" t="n"/>
+      <c r="E10" s="17" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="10" t="n"/>
+      <c r="J10" s="18" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="19" t="n"/>
+      <c r="E11" s="17" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="10" t="n"/>
+      <c r="J11" s="18" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="19" t="n"/>
+      <c r="E12" s="17" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="10" t="n"/>
+      <c r="J12" s="18" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="19" t="n"/>
+      <c r="E13" s="17" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="10" t="n"/>
+      <c r="J13" s="18" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="n"/>
-      <c r="E14" s="19" t="n"/>
+      <c r="E14" s="17" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="10" t="n"/>
+      <c r="J14" s="18" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="19" t="n"/>
+      <c r="E15" s="17" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="10" t="n"/>
+      <c r="J15" s="18" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="19" t="n"/>
+      <c r="E16" s="17" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="10" t="n"/>
+      <c r="J16" s="18" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="19" t="n"/>
+      <c r="E17" s="17" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="10" t="n"/>
+      <c r="J17" s="18" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="19" t="n"/>
+      <c r="E18" s="17" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="10" t="n"/>
+      <c r="J18" s="18" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="19" t="n"/>
+      <c r="E19" s="17" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="10" t="n"/>
+      <c r="J19" s="18" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="19" t="n"/>
+      <c r="E20" s="17" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="10" t="n"/>
+      <c r="J20" s="18" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="19" t="n"/>
+      <c r="E21" s="17" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="10" t="n"/>
+      <c r="J21" s="18" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="5" t="n"/>
-      <c r="E22" s="19" t="n"/>
+      <c r="E22" s="17" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="10" t="n"/>
+      <c r="J22" s="18" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="5" t="n"/>
-      <c r="E23" s="19" t="n"/>
+      <c r="E23" s="17" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="6" t="n"/>
-      <c r="J23" s="10" t="n"/>
+      <c r="J23" s="18" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="19" t="n"/>
+      <c r="E24" s="17" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="6" t="n"/>
-      <c r="J24" s="10" t="n"/>
+      <c r="J24" s="18" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="19" t="n"/>
+      <c r="E25" s="17" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="6" t="n"/>
-      <c r="J25" s="10" t="n"/>
+      <c r="J25" s="18" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="5" t="n"/>
-      <c r="E26" s="19" t="n"/>
+      <c r="E26" s="17" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="6" t="n"/>
-      <c r="J26" s="10" t="n"/>
+      <c r="J26" s="18" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="5" t="n"/>
-      <c r="E27" s="19" t="n"/>
+      <c r="E27" s="17" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="6" t="n"/>
-      <c r="J27" s="10" t="n"/>
+      <c r="J27" s="18" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="5" t="n"/>
-      <c r="E28" s="19" t="n"/>
+      <c r="E28" s="17" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="6" t="n"/>
-      <c r="J28" s="10" t="n"/>
+      <c r="J28" s="18" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="19" t="n"/>
+      <c r="E29" s="17" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="6" t="n"/>
-      <c r="J29" s="10" t="n"/>
+      <c r="J29" s="18" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="19" t="n"/>
+      <c r="E30" s="17" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="6" t="n"/>
-      <c r="J30" s="10" t="n"/>
+      <c r="J30" s="18" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="5" t="n"/>
-      <c r="E31" s="19" t="n"/>
+      <c r="E31" s="17" t="n"/>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="6" t="n"/>
-      <c r="J31" s="10" t="n"/>
+      <c r="J31" s="18" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="5" t="n"/>
-      <c r="E32" s="19" t="n"/>
+      <c r="E32" s="17" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="6" t="n"/>
-      <c r="J32" s="10" t="n"/>
+      <c r="J32" s="18" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="5" t="n"/>
-      <c r="E33" s="19" t="n"/>
+      <c r="E33" s="17" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="6" t="n"/>
-      <c r="J33" s="10" t="n"/>
+      <c r="J33" s="18" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="5" t="n"/>
-      <c r="E34" s="19" t="n"/>
+      <c r="E34" s="17" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="7" t="n"/>
       <c r="I34" s="6" t="n"/>
-      <c r="J34" s="10" t="n"/>
+      <c r="J34" s="18" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="19" t="n"/>
+      <c r="E35" s="17" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="6" t="n"/>
-      <c r="J35" s="10" t="n"/>
+      <c r="J35" s="18" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="19" t="n"/>
+      <c r="E36" s="17" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="6" t="n"/>
-      <c r="J36" s="10" t="n"/>
+      <c r="J36" s="18" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="19" t="n"/>
+      <c r="E37" s="17" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="6" t="n"/>
-      <c r="J37" s="10" t="n"/>
+      <c r="J37" s="18" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="5" t="n"/>
-      <c r="E38" s="19" t="n"/>
+      <c r="E38" s="17" t="n"/>
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="7" t="n"/>
       <c r="I38" s="6" t="n"/>
-      <c r="J38" s="10" t="n"/>
+      <c r="J38" s="18" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="5" t="n"/>
-      <c r="E39" s="19" t="n"/>
+      <c r="E39" s="17" t="n"/>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="6" t="n"/>
-      <c r="J39" s="10" t="n"/>
+      <c r="J39" s="18" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="5" t="n"/>
-      <c r="E40" s="19" t="n"/>
+      <c r="E40" s="17" t="n"/>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="6" t="n"/>
-      <c r="J40" s="10" t="n"/>
+      <c r="J40" s="18" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="5" t="n"/>
-      <c r="E41" s="19" t="n"/>
+      <c r="E41" s="17" t="n"/>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="6" t="n"/>
-      <c r="J41" s="10" t="n"/>
+      <c r="J41" s="18" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="5" t="n"/>
-      <c r="E42" s="19" t="n"/>
+      <c r="E42" s="17" t="n"/>
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="n"/>
       <c r="I42" s="6" t="n"/>
-      <c r="J42" s="10" t="n"/>
+      <c r="J42" s="18" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="5" t="n"/>
-      <c r="E43" s="19" t="n"/>
+      <c r="E43" s="17" t="n"/>
       <c r="F43" s="5" t="n"/>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="6" t="n"/>
-      <c r="J43" s="10" t="n"/>
+      <c r="J43" s="18" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="5" t="n"/>
-      <c r="E44" s="19" t="n"/>
+      <c r="E44" s="17" t="n"/>
       <c r="F44" s="5" t="n"/>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="7" t="n"/>
       <c r="I44" s="6" t="n"/>
-      <c r="J44" s="10" t="n"/>
+      <c r="J44" s="18" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>条件②の目安　○＝自分の観点を示し、本文の根拠を引いて主張した　△＝発言したが根拠が本文に届かない　×＝発言していない</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="20" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="20" t="n"/>
-      <c r="H46" s="20" t="n"/>
-      <c r="I46" s="20" t="n"/>
-      <c r="J46" s="20" t="n"/>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="19" t="n"/>
+      <c r="J46" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
